--- a/data/trans_orig/IP25A02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31689</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42372</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40218</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62454</t>
+          <t>62779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78563</t>
+          <t>79247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>35204</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36311</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>32223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52173</t>
+          <t>51524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57767</t>
+          <t>57037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81681</t>
+          <t>83090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57404</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77669</t>
+          <t>77615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58934</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81502</t>
+          <t>82442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122190</t>
+          <t>123210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152974</t>
+          <t>154185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>40693</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59593</t>
+          <t>59441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47548</t>
+          <t>47302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67771</t>
+          <t>67609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92193</t>
+          <t>92118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121387</t>
+          <t>119999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>29812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>47718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28129</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47835</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>72181</t>
+          <t>72451</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>103360</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60926</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83501</t>
+          <t>83239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80779</t>
+          <t>80477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>107198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148162</t>
+          <t>149282</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183645</t>
+          <t>183942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54461</t>
+          <t>55036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68132</t>
+          <t>66911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81813</t>
+          <t>81580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114491</t>
+          <t>114067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>31340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>47089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68000</t>
+          <t>66893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53615</t>
+          <t>54491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83869</t>
+          <t>84418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102212</t>
+          <t>101038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144716</t>
+          <t>145115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71304</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123964</t>
+          <t>125342</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>107244</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>147855</t>
+          <t>148527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>191403</t>
+          <t>193645</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>259862</t>
+          <t>262926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73338</t>
+          <t>72779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152233</t>
+          <t>151166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66214</t>
+          <t>67343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114561</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>152981</t>
+          <t>150425</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>244765</t>
+          <t>246195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>61475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,47 +3021,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>52450</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>39525</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>65771</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>52450</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>39431</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>67295</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81984</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118595</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104370</t>
+          <t>103093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145388</t>
+          <t>144303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146619</t>
+          <t>145773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189452</t>
+          <t>188250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263033</t>
+          <t>259037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>320881</t>
+          <t>319796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>222880</t>
+          <t>222479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281840</t>
+          <t>283602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281039</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>335667</t>
+          <t>337426</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>518944</t>
+          <t>526724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>604328</t>
+          <t>604336</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>199722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>281910</t>
+          <t>286551</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>205142</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>262559</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>418968</t>
+          <t>419302</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>517365</t>
+          <t>527651</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9702</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6029</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3039</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10334</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14505</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19308</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>29,53%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12031</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7605</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17358</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,96%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27855</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23139</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32875</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>66,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36860</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31391</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42234</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>65,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28550</t>
+          <t>27290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71061</t>
+          <t>60865</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62779</t>
+          <t>53997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79247</t>
+          <t>66944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11361</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18263</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11695</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6631</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>17871</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26035</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35204</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35826</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27757</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44730</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28088</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20884</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36715</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40533</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51524</t>
+          <t>34032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68621</t>
+          <t>62261</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57037</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83090</t>
+          <t>75074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60722</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50794</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69733</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>66986</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56768</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77615</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70432</t>
+          <t>61262</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82442</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>137418</t>
+          <t>121984</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123210</t>
+          <t>108113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154185</t>
+          <t>136189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49613</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41281</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59859</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48985</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40693</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>59441</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>38,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57248</t>
+          <t>43796</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47302</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67609</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>106233</t>
+          <t>93408</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92118</t>
+          <t>81577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119999</t>
+          <t>106210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>155754</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>155754</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>155754</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>142261</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>142261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>142261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>299783</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>299783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>299783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9341</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18552</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11978</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29812</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>31938</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23986</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47161</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>35964</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>59676</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>29,82%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>37052</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>27940</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>47916</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49713</t>
+          <t>35807</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39255</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60884</t>
+          <t>45801</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>86764</t>
+          <t>82968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>72451</t>
+          <t>69341</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103360</t>
+          <t>98166</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>89922</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>76200</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>102420</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>72327</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61252</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>83239</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>93878</t>
+          <t>75065</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80477</t>
+          <t>63764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107198</t>
+          <t>85784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>166205</t>
+          <t>164988</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149282</t>
+          <t>148827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183942</t>
+          <t>182736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>47736</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37606</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>60308</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>44393</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34602</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>55036</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>53130</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>36939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66911</t>
+          <t>56814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>97523</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81580</t>
+          <t>79869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114067</t>
+          <t>109062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20099</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13191</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29901</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>14231</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7949</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>22475</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31340</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34872</t>
+          <t>35294</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>26496</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47089</t>
+          <t>47889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>69229</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55493</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>84573</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>29,05%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>54034</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>37130</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>66893</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>69262</t>
+          <t>56455</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84418</t>
+          <t>69035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>125684</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101038</t>
+          <t>108485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145115</t>
+          <t>143571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>126147</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>107414</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>143225</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>43,33%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>49,19%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>105367</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>70573</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>125342</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>128175</t>
+          <t>103268</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107244</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148527</t>
+          <t>118337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>233542</t>
+          <t>229414</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193645</t>
+          <t>206380</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>262926</t>
+          <t>254703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>75665</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>59827</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>99571</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>25,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>96804</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>72779</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>151166</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>35,8%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>85944</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67343</t>
+          <t>62541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117982</t>
+          <t>88340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>182748</t>
+          <t>152194</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150425</t>
+          <t>132414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246195</t>
+          <t>178289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>291139</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>291139</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>291139</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>270436</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>270436</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>270436</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>304022</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>304022</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304022</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>574459</t>
+          <t>542586</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>574459</t>
+          <t>542586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>574459</t>
+          <t>542586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>47629</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>36319</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>61615</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>45624</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>34761</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>61475</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>55033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>76024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>109243</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>158108</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>137594</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>179232</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>125203</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>103093</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>144303</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>166507</t>
+          <t>124058</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>145773</t>
+          <t>107799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>188250</t>
+          <t>142008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>291710</t>
+          <t>282166</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259037</t>
+          <t>257296</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>319796</t>
+          <t>310418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>291296</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>266619</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>314806</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>362</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>256711</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>222479</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>283602</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>33,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>43,33%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>309313</t>
+          <t>250935</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281346</t>
+          <t>227881</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>337426</t>
+          <t>271774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>566024</t>
+          <t>542231</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>526724</t>
+          <t>513264</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>604336</t>
+          <t>574859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>200868</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>180845</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>228946</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>227042</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>199722</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>286551</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>230524</t>
+          <t>199680</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>179973</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>221831</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>400548</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>419302</t>
+          <t>371779</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>527651</t>
+          <t>433215</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
